--- a/test_env/Estado_Processos_Recebimento.xlsx
+++ b/test_env/Estado_Processos_Recebimento.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
@@ -577,51 +577,57 @@
       <c r="E2" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ORCAMENTO</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>COMPLETO</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Alessandro Cappi": 0.010000000000000002}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Alessandro Cappi": 1.0}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 5000.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 5000.0, "soma_ponderada": 50.00000000000001, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 5000.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 5000.0, "soma_ponderada": 5000.0, "fcmp_final": 1.0}}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Alessandro Cappi</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="n">
         <v>45870</v>
       </c>
@@ -632,11 +638,11 @@
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>45995.68281693044</v>
+        <v>46000.5783992941</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": NaN}</t>
+          <t>{"Alessandro Cappi": 10.000000000000002}</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
